--- a/bankole_sex_specific_splicing_2026/documentation/01_summarized_fiveSpecies_documentation_05ksb.xlsx
+++ b/bankole_sex_specific_splicing_2026/documentation/01_summarized_fiveSpecies_documentation_05ksb.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="59">
   <si>
     <t xml:space="preserve">Process for creating fiveSpecies GTF, lists documentation and necessary output</t>
   </si>
@@ -169,6 +169,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">REF/dmel_fb650/  
 </t>
@@ -180,6 +181,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dmel650_2_dmel6.gtf
 </t>
@@ -190,6 +192,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dmel650_2_dmel6_gffcompare_gene_key.csv
 dmel650_2_dmel6_compare_transcript_gene_assignment.csv
@@ -204,6 +207,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dsimWXD_2_dsim2.gtf
 </t>
@@ -214,6 +218,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dsimWXD_2_dsim2_gffcompare_gene_key.csv 
 REF/dsim_fb202/
@@ -226,6 +231,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dsim202_2_dsim2.gtf 
 </t>
@@ -236,6 +242,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dsim202_2_dsim2_gffcompare_gene_key.csv
 dsim202_2_dsim2_flag_ambig_gene.csv
@@ -250,6 +257,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dsan11_2_dsan1.gtf
 </t>
@@ -260,6 +268,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dsan11_2_dsan1_gffcompare_gene_key.csv
 dsan11_2_dsan1_flag_ambig_gene.csv
@@ -274,6 +283,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dyak21_2_dyak2.gtf
 </t>
@@ -284,6 +294,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dyak21_2_dyak2_gffcompare_gene_key.csv
 dyak21_2_dyak2_flag_ambig_gene.csv
@@ -298,6 +309,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dser11_2_dser1.gtf
 </t>
@@ -308,6 +320,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">dser11_2_dser1_gffcompare_gene_key.csv
 dser11_2_dser1_compare_transcript_gene_assignment.csv
@@ -432,6 +445,7 @@
         <sz val="11"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Create the fiveSpecies annotation
 </t>
@@ -442,6 +456,7 @@
         <sz val="11"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">For each genome:
 </t>
@@ -451,6 +466,7 @@
         <sz val="11"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1) Cat and select the longest unique UJC from all UJC GTF files that were mapped onto that genome.  
 2) Output into a single output GTF. 
@@ -482,12 +498,17 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">MCLAB/sex_specific_splicing/documentation/fiveSpecies_anno_and_assoc_files/
+create_fiveSpecies_flag_file_04ksb.xlsx</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Final version of the flag file is created  during ERP creation (summarized_ERP_analysis_documentation row 16)
 </t>
@@ -497,6 +518,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Example Columns:
 </t>
@@ -507,6 +529,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -516,6 +539,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">geneID
 dmel6_jxnhash
@@ -541,6 +565,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -562,6 +587,7 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -569,6 +595,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -576,6 +603,7 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -583,6 +611,7 @@
       <color rgb="FF808080"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -590,6 +619,7 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <u val="single"/>
@@ -597,6 +627,7 @@
       <color rgb="FF0000EE"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -606,29 +637,34 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFCC0000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -636,6 +672,7 @@
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -643,17 +680,20 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <u val="single"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1048,7 +1088,7 @@
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="5"/>
     </row>
-    <row r="2" customFormat="false" ht="57.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1100,7 @@
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="5"/>
     </row>
-    <row r="4" customFormat="false" ht="43.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1130,7 +1170,7 @@
       <c r="AMI9" s="12"/>
       <c r="AMJ9" s="12"/>
     </row>
-    <row r="10" s="2" customFormat="true" ht="57.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" s="2" customFormat="true" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,7 +1202,7 @@
       <c r="AMI11" s="1"/>
       <c r="AMJ11" s="1"/>
     </row>
-    <row r="12" s="2" customFormat="true" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" s="2" customFormat="true" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
@@ -1191,7 +1231,7 @@
       <c r="AMI13" s="1"/>
       <c r="AMJ13" s="1"/>
     </row>
-    <row r="14" s="2" customFormat="true" ht="127.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="2" customFormat="true" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>18</v>
       </c>
@@ -1223,7 +1263,7 @@
       <c r="AMI15" s="1"/>
       <c r="AMJ15" s="1"/>
     </row>
-    <row r="16" s="2" customFormat="true" ht="322.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="2" customFormat="true" ht="293.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -1253,7 +1293,7 @@
       <c r="AMI17" s="1"/>
       <c r="AMJ17" s="1"/>
     </row>
-    <row r="18" s="2" customFormat="true" ht="224.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="2" customFormat="true" ht="204.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -1283,7 +1323,7 @@
       <c r="AMI19" s="1"/>
       <c r="AMJ19" s="1"/>
     </row>
-    <row r="20" s="2" customFormat="true" ht="461.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="2" customFormat="true" ht="420.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -1313,7 +1353,7 @@
       <c r="AMI21" s="1"/>
       <c r="AMJ21" s="1"/>
     </row>
-    <row r="22" s="2" customFormat="true" ht="350.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" s="2" customFormat="true" ht="318.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -1360,7 +1400,7 @@
     <row r="25" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AMJ25" s="1"/>
     </row>
-    <row r="26" s="2" customFormat="true" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" s="2" customFormat="true" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
@@ -1390,7 +1430,7 @@
       <c r="AMI27" s="1"/>
       <c r="AMJ27" s="1"/>
     </row>
-    <row r="28" s="2" customFormat="true" ht="364.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" s="2" customFormat="true" ht="331.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
@@ -1430,7 +1470,7 @@
       <c r="AMI30" s="1"/>
       <c r="AMJ30" s="1"/>
     </row>
-    <row r="31" s="2" customFormat="true" ht="364.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" s="2" customFormat="true" ht="331.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>44</v>
       </c>
@@ -1539,7 +1579,7 @@
       <c r="AMI38" s="12"/>
       <c r="AMJ38" s="12"/>
     </row>
-    <row r="39" s="2" customFormat="true" ht="169.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" s="2" customFormat="true" ht="183.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>54</v>
       </c>
@@ -1547,13 +1587,13 @@
         <v>55</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AME39" s="4"/>
       <c r="AMF39" s="4"/>
@@ -1574,7 +1614,7 @@
     <row r="41" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12"/>
       <c r="D41" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AME41" s="11"/>
       <c r="AMF41" s="11"/>
